--- a/output/pdf_financials_xlsx/TRX.xlsx
+++ b/output/pdf_financials_xlsx/TRX.xlsx
@@ -5330,10 +5330,10 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.743773</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.805097</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -5342,19 +5342,19 @@
         <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.286</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.525</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>10.507</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>10.851</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.478</v>
       </c>
     </row>
     <row r="93">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-8.117000000000001</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0.229</v>
@@ -6719,10 +6719,10 @@
         <v>-1.864</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.417</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.913</v>
       </c>
     </row>
     <row r="119">
@@ -9600,7 +9600,11 @@
           <t>Share-based payments reserve 16</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -9678,7 +9682,11 @@
           <t>Warrants reserve 17</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11184,7 +11192,11 @@
           <t>Share-based payments reserve 15</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -11264,7 +11276,11 @@
           <t>Warrants reserve 16</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13090,7 +13106,11 @@
           <t>Share based payment reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -13174,7 +13194,11 @@
           <t>Warrants reserve (Note 17)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15244,7 +15268,11 @@
           <t>Share based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -15328,7 +15356,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -17652,7 +17684,11 @@
           <t>Exploration and evaluation assets and expenditures $</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -19100,7 +19136,11 @@
           <t>Exploration and evaluation assets and expenditures $</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -22286,7 +22326,11 @@
           <t>Exploration and evaluation assets and expenditures</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRX.xlsx
+++ b/output/pdf_financials_xlsx/TRX.xlsx
@@ -2282,19 +2282,19 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>13.447</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>7.629</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.331</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="35">
@@ -2384,19 +2384,19 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>13.447</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>7.629</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.331</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="37">
@@ -2996,19 +2996,19 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>13.779</v>
+        <v>0.332</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>7.182</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>9.092000000000001</v>
+        <v>1.463</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>9.577</v>
+        <v>1.246</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.007</v>
+        <v>1.237</v>
       </c>
     </row>
     <row r="49">
@@ -7054,13 +7054,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.115</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-1.229</v>
       </c>
     </row>
     <row r="125">
@@ -7109,13 +7109,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.115</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-1.229</v>
       </c>
     </row>
     <row r="126">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -18202,7 +18202,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -19734,7 +19738,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRX.xlsx
+++ b/output/pdf_financials_xlsx/TRX.xlsx
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.448036</v>
+        <v>0.885603</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.469575</v>
+        <v>0.916502</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.48965</v>
+        <v>0.87134</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.388675</v>
+        <v>0.7640169999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>380.631</v>
+        <v>757.0650000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>326.088</v>
+        <v>693.612</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.01183</v>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
@@ -7416,15 +7416,11 @@
       <c r="M130" s="3" t="n">
         <v>8.476000000000001</v>
       </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N130" s="3" t="n">
+        <v>7.629</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>8.331</v>
       </c>
     </row>
     <row r="131">
@@ -7585,15 +7581,11 @@
       <c r="M133" s="3" t="n">
         <v>7.629</v>
       </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N133" s="3" t="n">
+        <v>8.331</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>7.77</v>
       </c>
     </row>
     <row r="134">
@@ -9192,7 +9184,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10942,7 +10938,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -18466,7 +18466,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -18550,7 +18554,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -20002,7 +20010,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -20086,7 +20098,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -20254,7 +20270,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -28652,7 +28672,11 @@
           <t>Proceeds onshort-term investment</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -35140,7 +35164,11 @@
           <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -38362,7 +38390,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E360" s="5" t="n">
         <v>0.437567</v>
       </c>
